--- a/Result/profitability/3597.xlsx
+++ b/Result/profitability/3597.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM53"/>
+  <dimension ref="A1:AM54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.11</v>
       </c>
       <c r="M2" t="n">
-        <v>0.18875</v>
+        <v>0.17</v>
       </c>
       <c r="N2" t="n">
-        <v>23.33875</v>
+        <v>23.03125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.12375</v>
+        <v>0.08750000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>22.39375</v>
+        <v>22.3575</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04375</v>
+        <v>0.055</v>
       </c>
       <c r="N4" t="n">
-        <v>21.26125</v>
+        <v>21.51375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.42</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07375000000000001</v>
+        <v>0.14375</v>
       </c>
       <c r="N5" t="n">
-        <v>20.6325</v>
+        <v>20.9175</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0.23625</v>
+        <v>0.24125</v>
       </c>
       <c r="N6" t="n">
-        <v>20.07625</v>
+        <v>20.08</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.36</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1625</v>
+        <v>0.16875</v>
       </c>
       <c r="N7" t="n">
-        <v>18.8475</v>
+        <v>18.7775</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -7159,6 +7159,133 @@
       </c>
       <c r="AM53" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>3597</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>253</v>
+      </c>
+      <c r="D54" t="n">
+        <v>191</v>
+      </c>
+      <c r="E54" t="n">
+        <v>62</v>
+      </c>
+      <c r="F54" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="G54" t="n">
+        <v>19</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>7.43%</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J54" t="n">
+        <v>17</v>
+      </c>
+      <c r="K54" t="n">
+        <v>10</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.20875</v>
+      </c>
+      <c r="N54" t="n">
+        <v>24.13125</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="X54" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0.0779392338177014</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>-1.931034482758621</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>2.280000000000001</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.1027027027027028</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK54" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
